--- a/public/folhas/folha-evento.xlsx
+++ b/public/folhas/folha-evento.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Evento" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="Relatório de evento" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
